--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86131\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA104A9-52C2-4554-B314-2565A00A4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C481823-3808-408B-9092-6FD5F0A5F260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>序号</t>
   </si>
@@ -47,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -71,6 +71,17 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -115,14 +126,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -442,58 +462,48 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="16.6640625" customWidth="1"/>
+    <col min="1" max="6" width="16.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86131\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C481823-3808-408B-9092-6FD5F0A5F260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79603A0-0E47-4DCE-B615-151D6C009ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>序号</t>
   </si>
@@ -40,14 +40,15 @@
     <t>备注</t>
   </si>
   <si>
-    <t/>
+    <t>(例如1.1,序号不能为空)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -81,6 +82,12 @@
       <sz val="10"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -126,7 +133,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -143,6 +150,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -459,10 +469,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="16.6640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="27.21875" style="3" customWidth="1"/>
+    <col min="2" max="6" width="16.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -486,27 +497,15 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
       <c r="E2" s="4"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importKcsjEngineeringQuantitiesBillDetail.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86131\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79603A0-0E47-4DCE-B615-151D6C009ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9306F5-B03C-43ED-9E3D-F54E6AD96656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>序号</t>
   </si>
@@ -38,10 +38,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>(例如1.1,序号不能为空)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -497,9 +493,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="5"/>
@@ -508,6 +502,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="格式" prompt="例如1.1，序号不能为空" sqref="A1:A1048576" xr:uid="{3AD12768-A87B-487C-A804-C4B22C466F43}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>